--- a/apps/worker/samples/품질관련 코드표.xlsx
+++ b/apps/worker/samples/품질관련 코드표.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="140">
   <si>
     <t>2차 분류 (중분류)</t>
   </si>
@@ -232,16 +232,19 @@
     <t>품질관리비 사용내역서</t>
   </si>
   <si>
+    <t>506</t>
+  </si>
+  <si>
     <t>공인기관성적서</t>
   </si>
   <si>
-    <t>506</t>
+    <t>507</t>
   </si>
   <si>
     <t>철근시험성적서</t>
   </si>
   <si>
-    <t>507</t>
+    <t>508</t>
   </si>
   <si>
     <t>레미콘 자재인수검사성적서</t>
@@ -253,10 +256,13 @@
     <t>공인기관시험의뢰서/성적서</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>PC부재-공장품질서류</t>
   </si>
   <si>
-    <t>510</t>
+    <t>511</t>
   </si>
   <si>
     <t>케미칼앙카인발시험</t>
@@ -1192,316 +1198,316 @@
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
